--- a/results/job_matches_2026-10-08.xlsx
+++ b/results/job_matches_2026-10-08.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,12 +526,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -540,33 +540,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf6cb804310788f</t>
+          <t>https://www.indeed.com/viewjob?jk=d52bde6426b7b2e8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52bde6426b7b2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2948fbe9d2340fca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2948fbe9d2340fca</t>
+          <t>https://www.indeed.com/viewjob?jk=b28eca491f11ed83</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>AWS Cloud Application Architect - Green Card or US Citizen only</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28eca491f11ed83</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5f5b54c50c4894</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Cloud Application Architect - Green Card or US Citizen only</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GroundWork Renewables, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5f5b54c50c4894</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6dd2f1d6844211</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Agentic AI Engineer – Snowflake</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GroundWork Renewables, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6dd2f1d6844211</t>
+          <t>https://www.indeed.com/viewjob?jk=c24d04fca23f04a4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AWS Agentic AI Engineer – Snowflake</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24d04fca23f04a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5dc654cacc73fe</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Java + Python Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,34 +824,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac695015f6e52803</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6f8733c3935b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java + Python Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,34 +859,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Snowflake, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6f8733c3935b</t>
+          <t>https://www.indeed.com/viewjob?jk=21725d4d5a969dd0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,52 +894,52 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Scala, Kafka, PostgreSQL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88c40e681df4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=415b6d66e75228d2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Fraud Risk Modeling</t>
+          <t>Platform Engineer Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1b0bc837735bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=98d8a4cf8d1aaf1e</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>engineer sr - ST (Hybrid) Seattle WA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Howard Hughes Medical Institute</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,34 +999,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Spark</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c5e1818487b920</t>
+          <t>https://www.indeed.com/viewjob?jk=679a365e45ca5a6c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C++, Python, Golang Developer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Predictive Sales A.I.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Dask, Polars, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e59d8791104d6b59</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1a6eaf40c260e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C,C++, Python, Golang Developer</t>
+          <t>AJAY K- SOLUTION ARCHITECT | CLOUD, DATA, INTEGRATION &amp; AI-ENABLED PLATFORMS.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cassco International, Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,34 +1069,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aaed4db41a0b1f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9af1985824c8bc86</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>C,C++, Python, Golang Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Predictive Sales A.I.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Dask, Polars, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1a6eaf40c260e</t>
+          <t>https://www.indeed.com/viewjob?jk=3aaed4db41a0b1f5</t>
         </is>
       </c>
     </row>
@@ -1156,25 +1156,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Amarillo, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abeb02a0e515f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=25c51b626d77472c</t>
         </is>
       </c>
     </row>
@@ -1226,17 +1226,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>Novacis Digital</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,34 +1244,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb015cbf7890d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2798550649837e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Loveland, CO)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Antech Diagnostics</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loveland, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,32 +1289,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12afaeb4d5194deb</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c99bf247866440</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Platform Engineer/DevOp</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,94 +1324,94 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c13abcae168f92</t>
+          <t>https://www.indeed.com/viewjob?jk=eb015cbf7890d8a1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de63d204e832110a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea336bd03fc8adb1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876322e831ec8eca</t>
+          <t>https://www.indeed.com/viewjob?jk=b15a9d448062578a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer/DevOp</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,34 +1419,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c07ba22730cc31c</t>
+          <t>https://www.indeed.com/viewjob?jk=03c13abcae168f92</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Database Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>BerryDunn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, MySQL, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d993410e2b916af</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc69b0c8fcdb4fa</t>
         </is>
       </c>
     </row>
@@ -1506,25 +1506,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c1b2b06cb6b3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=aa3a48755605f28e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,32 +1569,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ccd4f80fb807bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=68f070fab73c645f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4728a5662dc7585</t>
+          <t>https://www.indeed.com/viewjob?jk=acdebbbdc22b8477</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6553285bc3649a</t>
+          <t>https://www.indeed.com/viewjob?jk=543fff0177376c1b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>FedEx Dataworks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c365530d5e90342</t>
+          <t>https://www.indeed.com/viewjob?jk=75c1b2b06cb6b3d3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f610986642a7b2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c365530d5e90342</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer II, Marketing Technology - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,17 +1734,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238a27c5210ae789</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f610986642a7b2</t>
         </is>
       </c>
     </row>
@@ -1786,17 +1786,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Architecture &amp; Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Formlabs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau</t>
+          <t>Redshift, IAM, RDS, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923379e0dc0b8dde</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e3bb316c3ab91</t>
         </is>
       </c>
     </row>
@@ -1996,17 +1996,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer (Remote)</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Revenue Management Solutions</t>
+          <t>FedEx Dataworks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,32 +2024,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83625117c0bb978</t>
+          <t>https://www.indeed.com/viewjob?jk=7ccd4f80fb807bf1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>FedEx Dataworks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81c606945103730</t>
+          <t>https://www.indeed.com/viewjob?jk=b4728a5662dc7585</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Agama Solutions</t>
+          <t>FedEx Dataworks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7575f45f137226ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ad6553285bc3649a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Information Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Agama Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,34 +2119,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Databricks, GCP, MLOps, MLflow</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bee6defc91ca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=7575f45f137226ab</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>District Integration &amp; Support Engineer (Systems Engineer I) - 61161120</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>ImagineSoftware</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Talend, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Spark, Scala, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ffc90f30b5ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5dc68f6ea04512</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Full-Stack Engineer 4 (SQL Server DBA)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,32 +2199,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57b9b0b5d74551c</t>
+          <t>https://www.indeed.com/viewjob?jk=f393fa8d32e16893</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>District Integration &amp; Support Engineer (Systems Engineer I) - 61161120</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Talend, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,67 +2234,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2567da3c97e0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ffc90f30b5ea7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Senior Data Engineer</t>
+          <t>Sr. Data Scientist Job</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16371cbe9a6f6a94</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfe23127b82b76c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b4524a4f891c31</t>
+          <t>https://www.indeed.com/viewjob?jk=b81c606945103730</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Integration Analyst</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b236860653562b</t>
+          <t>https://www.indeed.com/viewjob?jk=a57b9b0b5d74551c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Analyst</t>
+          <t>Service Delivery Center, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d208d296c27320</t>
+          <t>https://www.indeed.com/viewjob?jk=16371cbe9a6f6a94</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,34 +2399,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57923c372a91491</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2567da3c97e0c2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,77 +2434,77 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
+          <t>Lambda, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd1157f032a62ba</t>
+          <t>https://www.indeed.com/viewjob?jk=53b4524a4f891c31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Wireless Engineer</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DMI</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Crownsville, MD, US USA</t>
+          <t>Chelmsford, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fcbfb44e8f3307</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a5dfa62a0d990</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,32 +2514,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f951e4e29fe69c66</t>
+          <t>https://www.indeed.com/viewjob?jk=e7da1ea0ad17289e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b09df58bdb608c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6fffdae1534f271</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7d27339ccef1f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0564e4c963eeaa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IT Analyst III - Cloud Automation and Platform Engineer</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Taylorsville, UT, US USA</t>
+          <t>Rocklin, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9184edf09372f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=64568d42f66cc32c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Vision Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rezilient Health</t>
+          <t>Targan INC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Hive, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,67 +2654,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba5d9d223a8fba0</t>
+          <t>https://www.indeed.com/viewjob?jk=8982f49fab0f79cf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Data Integration Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nuuly</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Zookeeper, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c18e77b373c042e</t>
+          <t>https://www.indeed.com/viewjob?jk=18b236860653562b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Strategy and Engineering</t>
+          <t>Full-Stack Engineer 4 (Java, Kafka, AWS)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a660c8397fa50076</t>
+          <t>https://www.indeed.com/viewjob?jk=246675a88211c8be</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Integration Engineer 4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,24 +2759,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bd8d73e2e92638</t>
+          <t>https://www.indeed.com/viewjob?jk=00c18c2f7ae91a00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer – Azure Practitioner</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KCI Technologies</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,34 +2784,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d231129436df5d79</t>
+          <t>https://www.indeed.com/viewjob?jk=31e7731f1f9f1fba</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,34 +2819,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a7de6eda101af3</t>
+          <t>https://www.indeed.com/viewjob?jk=f951e4e29fe69c66</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer III - ETL</t>
+          <t>IT Analyst III - Cloud Automation and Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Taylorsville, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, NoSQL, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,32 +2864,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b8fa5e3eb4a90c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9184edf09372f2a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, MongoDB, Cassandra, Docker, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,32 +2899,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54fe6ade52e7b03</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b09df58bdb608c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Applied AI &amp; Integrations Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Rezilient Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Docker, Kubernetes, Git, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,102 +2934,102 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be186d5b6e7e5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba5d9d223a8fba0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full stack software engineer</t>
+          <t>Nuuly - Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Nuuly</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Zookeeper, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef7970decc80bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7c18e77b373c042e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - CTO innovations</t>
+          <t>Site Reliability Engineer III – AI-Centric Application Performance &amp; FinOps</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb6bdbcc89b8901</t>
+          <t>https://www.indeed.com/viewjob?jk=acc60f244ee03aef</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Snowflake</t>
+          <t>Data Engineer III - ETL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, NoSQL, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3039,32 +3039,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e479aec834dda7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=48b8fa5e3eb4a90c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Snowflake</t>
+          <t>Analytics Engineering Solutions Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>UnityPoint Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
+          <t>AWS, S3, RDS, Azure, Cloud Storage, Scala, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,32 +3074,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac197ebe84b27d67</t>
+          <t>https://www.indeed.com/viewjob?jk=9285753a7bb4b789</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Clinician-Developer: Cloud &amp; Integrations</t>
+          <t>Senior Consultant - Data Strategy and Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Charleston Children’s Therapy Center</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, Docker, AKS</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,102 +3109,102 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf03acdee6bfb411</t>
+          <t>https://www.indeed.com/viewjob?jk=a660c8397fa50076</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (Hybrid)</t>
+          <t>Solutions Architect (Data)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6442e1547a870e80</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c96a2380ee98e7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Production Engineer - Realtime Products</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3250fba091a2092</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75f442e4703aad</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineering</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,67 +3214,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f18e8940a4968b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7d27339ccef1f0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business (Fintech)</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95aea0382d2db66</t>
+          <t>https://www.indeed.com/viewjob?jk=81a7de6eda101af3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MTS 1, Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,67 +3284,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389bda3afea947e0</t>
+          <t>https://www.indeed.com/viewjob?jk=98bd8d73e2e92638</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Quality Analyst</t>
+          <t>Full-Stack Software Engineer – Azure Practitioner</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Group</t>
+          <t>KCI Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f52a8d71cbe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d231129436df5d79</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Quality Analyst</t>
+          <t>Full-Stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3354,32 +3354,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064892ad293de829</t>
+          <t>https://www.indeed.com/viewjob?jk=2a0e6e498f727e5e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Quality Analyst</t>
+          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Linthicum, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3389,24 +3389,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23995c14ef6d4f73</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6e40de4c01a38c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Quality Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Group</t>
+          <t>Enhabit Home Health &amp; Hospice</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3424,24 +3424,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482a123ad569f8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fc5b4d516e7f51</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Quality Analyst</t>
+          <t>MTS 1, Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Group</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, MongoDB, Cassandra, Docker, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3459,24 +3459,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8de9417533fb28</t>
+          <t>https://www.indeed.com/viewjob?jk=b54fe6ade52e7b03</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Applied AI &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ALTEN</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Docker, Kubernetes, Git, Java</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3494,24 +3494,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177cc6a11c4d3854</t>
+          <t>https://www.indeed.com/viewjob?jk=be186d5b6e7e5d03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Full stack software engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3529,24 +3529,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3243df3687a8dab</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef7970decc80bb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Machine Learning Engineer - CTO innovations</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kalispell, MT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3564,24 +3564,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1635f185b01169a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb6bdbcc89b8901</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior DataBricks Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Onx Homes</t>
+          <t>NomiSo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3589,34 +3589,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977ace2d9d1e2ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7372a5249c25b1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Software Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3634,24 +3634,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f134c41ea48f5e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=e479aec834dda7f8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior Software Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bf19bd58d90737</t>
+          <t>https://www.indeed.com/viewjob?jk=ac197ebe84b27d67</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Clinician-Developer: Cloud &amp; Integrations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>Charleston Children’s Therapy Center</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3704,7 +3704,567 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f2e8afec7dbdbb</t>
+          <t>https://www.indeed.com/viewjob?jk=bf03acdee6bfb411</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Westchester Medical Center Health Network</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Valhalla, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6442e1547a870e80</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Data &amp; Integrations Engineering)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Cedar INC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1a64073f77de1fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Microsoft Dynamics 365 F&amp;O Data Architect</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Innova Software Services</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Talend</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99b94a3a4f9e025c</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Data/AI Engineering</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f18e8940a4968b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Digital Native Business (Fintech)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a95aea0382d2db66</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7348aaf9ea0dffed</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8839314f6759c131</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2db021d4795c74b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0feddabdba27405</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=389bda3afea947e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Data Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Group</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83f52a8d71cbe4d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Data Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Group</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=064892ad293de829</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Data Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Group</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Linthicum, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23995c14ef6d4f73</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Data Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Group</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=482a123ad569f8d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Data Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Group</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de8de9417533fb28</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer - Manufacturing Plant Floor Systems</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MLOps, CI/CD, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a23c424bcc5003c2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-08.xlsx
+++ b/results/job_matches_2026-10-08.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Texas City, TX, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -501,7 +501,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -536,7 +536,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -596,17 +596,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,34 +614,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28eca491f11ed83</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3c1554c10248b1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud Application Architect - Green Card or US Citizen only</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5f5b54c50c4894</t>
+          <t>https://www.indeed.com/viewjob?jk=b28eca491f11ed83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Application Architect - Green Card or US Citizen only</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GroundWork Renewables, Inc.</t>
+          <t>Nextiya</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6dd2f1d6844211</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5f5b54c50c4894</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AWS Agentic AI Engineer – Snowflake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GroundWork Renewables, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albuquerque, NM, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24d04fca23f04a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6dd2f1d6844211</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AWS Agentic AI Engineer – Snowflake</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Global High Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5dc654cacc73fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c24d04fca23f04a4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Leawood, KS, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,34 +789,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab03e483c84aee8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5dc654cacc73fe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java + Python Developer</t>
+          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6f8733c3935b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab03e483c84aee8</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Erlanger, KY, US USA</t>
+          <t>Erlanger, KY, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -981,17 +981,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>engineer sr - ST (Hybrid) Seattle WA</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Predictive Sales A.I.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Dask, Polars, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679a365e45ca5a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1a6eaf40c260e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>engineer sr - ST (Hybrid) Seattle WA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Predictive Sales A.I.</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Dask, Polars, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1a6eaf40c260e</t>
+          <t>https://www.indeed.com/viewjob?jk=679a365e45ca5a6c</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Farmington Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1121,17 +1121,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>C++, Python, Golang Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Predictive Sales A.I.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Dask, Polars, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c03750cbc30f39f</t>
+          <t>https://www.indeed.com/viewjob?jk=4079e0cd8f01503b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amarillo, TX, US USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c51b626d77472c</t>
+          <t>https://www.indeed.com/viewjob?jk=2abeb02a0e515f8a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Research Application Support Engineer - Remote</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,17 +1209,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd00f0bef8bd3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b919d7fa31ebc26</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Research Application Support Engineer - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c99bf247866440</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd00f0bef8bd3e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Eau Claire, WI, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb015cbf7890d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea336bd03fc8adb1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Orlando, FL, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea336bd03fc8adb1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb015cbf7890d8a1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Java Developer (Loveland, CO)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Antech Diagnostics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Loveland, CO, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>RDS, Azure, Kafka, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b15a9d448062578a</t>
+          <t>https://www.indeed.com/viewjob?jk=12afaeb4d5194deb</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1436,17 +1436,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Enterprise Database Administrator</t>
+          <t>SDC WAMT Back End Engineer---Analyst---Dallas, Raleigh, San Antonio</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BerryDunn</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, MySQL, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc69b0c8fcdb4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7c11d949a142a620</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SDC WAMT Back End Engineer---Analyst---Dallas, Raleigh, San Antonio</t>
+          <t>Senior Enterprise Database Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>BerryDunn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, ME, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, MySQL, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c11d949a142a620</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc69b0c8fcdb4fa</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1564,37 +1564,37 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f070fab73c645f</t>
+          <t>https://www.indeed.com/viewjob?jk=acdebbbdc22b8477</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DBA II</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>FedEx Dataworks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acdebbbdc22b8477</t>
+          <t>https://www.indeed.com/viewjob?jk=75c1b2b06cb6b3d3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DBA II</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=543fff0177376c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c365530d5e90342</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>McKinney, TX, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c1b2b06cb6b3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f610986642a7b2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Formlabs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>Redshift, IAM, RDS, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c365530d5e90342</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e3bb316c3ab91</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,14 +1744,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f610986642a7b2</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb72edaec6cad88</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer-5</t>
+          <t>Salesforce Developer with python-5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb72edaec6cad88</t>
+          <t>https://www.indeed.com/viewjob?jk=40fe46976f1c74ae</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SDC WAMT Senior Backend Engineer---Senior-----Dallas, Raleigh, San Antonio</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Formlabs</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e3bb316c3ab91</t>
+          <t>https://www.indeed.com/viewjob?jk=e65c5560ca576a10</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1891,17 +1891,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python-5</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DFUSE TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ai, OH, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,34 +1909,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40fe46976f1c74ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3ef12034fb6c8a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python-5</t>
+          <t>Quality Assurance Engineer (Remote)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Revenue Management Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Oklahoma City, OK, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,112 +1944,112 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bd4fe37ee6739a</t>
+          <t>https://www.indeed.com/viewjob?jk=a83625117c0bb978</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SDC WAMT Senior Backend Engineer---Senior-----Dallas, Raleigh, San Antonio</t>
+          <t>Advisor-Data Engineer MDM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65c5560ca576a10</t>
+          <t>https://www.indeed.com/viewjob?jk=efe237925fb7924c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Sr Advisor-Data Engineer MDM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ccd4f80fb807bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=f57eec5ffd5808ad</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>Agama Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Glendale, CA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4728a5662dc7585</t>
+          <t>https://www.indeed.com/viewjob?jk=7575f45f137226ab</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Lancaster, PA, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6553285bc3649a</t>
+          <t>https://www.indeed.com/viewjob?jk=b81c606945103730</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer 4 (SQL Server DBA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Agama Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Riverwoods, IL, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,42 +2119,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7575f45f137226ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f393fa8d32e16893</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ImagineSoftware</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,67 +2164,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a5dc68f6ea04512</t>
+          <t>https://www.indeed.com/viewjob?jk=a57b9b0b5d74551c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (SQL Server DBA)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Curant Health Georgia LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Smyrna, GA, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f393fa8d32e16893</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f2fb1b8f4b0f0b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>District Integration &amp; Support Engineer (Systems Engineer I) - 61161120</t>
+          <t>Service Delivery Center, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Talend, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,94 +2234,94 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ffc90f30b5ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=16371cbe9a6f6a94</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist Job</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Chelmsford, MA, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfe23127b82b76c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a5dfa62a0d990</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Vision Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Targan INC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Hive, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81c606945103730</t>
+          <t>https://www.indeed.com/viewjob?jk=8982f49fab0f79cf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Integration Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Fort Worth, TX, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57b9b0b5d74551c</t>
+          <t>https://www.indeed.com/viewjob?jk=18b236860653562b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Buffalo, NY, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,147 +2364,147 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>Lambda, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16371cbe9a6f6a94</t>
+          <t>https://www.indeed.com/viewjob?jk=53b4524a4f891c31</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Machine Learning Engineer-Xumo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, BigQuery, Spark, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2567da3c97e0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d075be1566febf4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Integration Engineer 4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Riverwoods, IL, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b4524a4f891c31</t>
+          <t>https://www.indeed.com/viewjob?jk=00c18c2f7ae91a00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Digital Banking Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>First Tech Federal Credit Union</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chelmsford, MA, US USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a5dfa62a0d990</t>
+          <t>https://www.indeed.com/viewjob?jk=31e7731f1f9f1fba</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Digital Banking Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>First Tech Federal Credit Union</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,32 +2514,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7da1ea0ad17289e</t>
+          <t>https://www.indeed.com/viewjob?jk=f951e4e29fe69c66</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Digital Banking Full Stack Engineer</t>
+          <t>IT Analyst III - Cloud Automation and Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>First Tech Federal Credit Union</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Taylorsville, UT, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fffdae1534f271</t>
+          <t>https://www.indeed.com/viewjob?jk=c9184edf09372f2a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Digital Banking Full Stack Engineer</t>
+          <t>Site Reliability Engineer III – AI-Centric Application Performance &amp; FinOps</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>First Tech Federal Credit Union</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0564e4c963eeaa</t>
+          <t>https://www.indeed.com/viewjob?jk=acc60f244ee03aef</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Digital Banking Full Stack Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>First Tech Federal Credit Union</t>
+          <t>Rational Dynamics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rocklin, CA, US USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64568d42f66cc32c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b09df58bdb608c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Vision Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Targan INC</t>
+          <t>Rezilient Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Hive, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,32 +2654,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8982f49fab0f79cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba5d9d223a8fba0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Integration Analyst</t>
+          <t>Data Engineer III - ETL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, NoSQL, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,59 +2689,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b236860653562b</t>
+          <t>https://www.indeed.com/viewjob?jk=48b8fa5e3eb4a90c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Kafka, AWS)</t>
+          <t>Senior Production Engineer - Realtime Products</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=246675a88211c8be</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75f442e4703aad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Integration Engineer 4</t>
+          <t>MTS 1, Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,24 +2759,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00c18c2f7ae91a00</t>
+          <t>https://www.indeed.com/viewjob?jk=98bd8d73e2e92638</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Consultant - Data Strategy and Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Clear Base Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cary, NC, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e7731f1f9f1fba</t>
+          <t>https://www.indeed.com/viewjob?jk=a660c8397fa50076</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eagan, MN, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,24 +2829,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f951e4e29fe69c66</t>
+          <t>https://www.indeed.com/viewjob?jk=81a7de6eda101af3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT Analyst III - Cloud Automation and Platform Engineer</t>
+          <t>Solutions Architect (Data)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Taylorsville, UT, US USA</t>
+          <t>MO, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9184edf09372f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c96a2380ee98e7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Tech-BAIN Service Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Universal Music Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,147 +2889,147 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b09df58bdb608c</t>
+          <t>https://www.indeed.com/viewjob?jk=b959e0e3c13d4ea3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rezilient Health</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Willow Grove, PA, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba5d9d223a8fba0</t>
+          <t>https://www.indeed.com/viewjob?jk=113b0ef7bbd43b1b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nuuly - Sr DevOps Engineer</t>
+          <t>MTS 1, Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nuuly</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Zookeeper, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, MongoDB, Cassandra, Docker, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c18e77b373c042e</t>
+          <t>https://www.indeed.com/viewjob?jk=b54fe6ade52e7b03</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III – AI-Centric Application Performance &amp; FinOps</t>
+          <t>Applied AI &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milwaukee, WI, USA USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Docker, Kubernetes, Git, Java</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc60f244ee03aef</t>
+          <t>https://www.indeed.com/viewjob?jk=be186d5b6e7e5d03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer III - ETL</t>
+          <t>Full stack software engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, USA USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, NoSQL, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3039,32 +3039,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b8fa5e3eb4a90c</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef7970decc80bb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineering Solutions Architect</t>
+          <t>Machine Learning Engineer - CTO innovations</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UnityPoint Health</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Cloud Storage, Scala, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,102 +3074,102 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9285753a7bb4b789</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb6bdbcc89b8901</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Strategy and Engineering</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Surge InfoTech LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Alexandria, VA, USA USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a660c8397fa50076</t>
+          <t>https://www.indeed.com/viewjob?jk=009031cd529e79e4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Architect (Data)</t>
+          <t>Senior DataBricks Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NomiSo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Scottsdale, AZ, USA USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c96a2380ee98e7</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7372a5249c25b1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Production Engineer - Realtime Products</t>
+          <t>Software Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Buffalo, NY, USA USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,32 +3179,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75f442e4703aad</t>
+          <t>https://www.indeed.com/viewjob?jk=e479aec834dda7f8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Buffalo, NY, USA USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,137 +3214,137 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7d27339ccef1f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ac197ebe84b27d67</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Sr. Software Engineer (Data &amp; Integrations Engineering)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>Cedar INC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Medallion Architecture, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a7de6eda101af3</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a64073f77de1fc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>VIE - Software Engineer (based in Miami)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Pelico</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bd8d73e2e92638</t>
+          <t>https://www.indeed.com/viewjob?jk=85b64e32ec1fb240</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer – Azure Practitioner</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KCI Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d231129436df5d79</t>
+          <t>https://www.indeed.com/viewjob?jk=389bda3afea947e0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4</t>
+          <t>Solutions Architect - Digital Native Business (Fintech)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>NJ, USA USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3354,32 +3354,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a0e6e498f727e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=a95aea0382d2db66</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, JavaScript)</t>
+          <t>Senior Data Quality Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Breakthru Beverage Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3389,24 +3389,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6e40de4c01a38c</t>
+          <t>https://www.indeed.com/viewjob?jk=83f52a8d71cbe4d7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Dynamics 365 F&amp;O Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Enhabit Home Health &amp; Hospice</t>
+          <t>Innova Software Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3414,34 +3414,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fc5b4d516e7f51</t>
+          <t>https://www.indeed.com/viewjob?jk=99b94a3a4f9e025c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Senior Data/AI Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, MongoDB, Cassandra, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3459,24 +3459,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54fe6ade52e7b03</t>
+          <t>https://www.indeed.com/viewjob?jk=8f18e8940a4968b5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Applied AI &amp; Integrations Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>ALTEN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Docker, Kubernetes, Git, Java</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3494,24 +3494,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be186d5b6e7e5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=177cc6a11c4d3854</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full stack software engineer</t>
+          <t>Sr. Systems Engineer - Manufacturing Plant Floor Systems</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3519,750 +3519,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MLOps, CI/CD, SonarQube, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef7970decc80bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer - CTO innovations</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, ELT, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb6bdbcc89b8901</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior DataBricks Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NomiSo</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7372a5249c25b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Engineer - Snowflake</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>M&amp;T Bank</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e479aec834dda7f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Snowflake</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>M&amp;T Bank</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac197ebe84b27d67</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Clinician-Developer: Cloud &amp; Integrations</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Charleston Children’s Therapy Center</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf03acdee6bfb411</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Westchester Medical Center Health Network</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Valhalla, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6442e1547a870e80</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Data &amp; Integrations Engineering)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Cedar INC</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a64073f77de1fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Microsoft Dynamics 365 F&amp;O Data Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Innova Software Services</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Talend</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99b94a3a4f9e025c</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data/AI Engineering</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f18e8940a4968b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Digital Native Business (Fintech)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a95aea0382d2db66</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7348aaf9ea0dffed</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8839314f6759c131</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2db021d4795c74b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0feddabdba27405</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389bda3afea947e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Data Quality Analyst</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Group</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83f52a8d71cbe4d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Data Quality Analyst</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Group</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=064892ad293de829</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Data Quality Analyst</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Group</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Linthicum, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23995c14ef6d4f73</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Data Quality Analyst</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Group</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=482a123ad569f8d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Data Quality Analyst</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Group</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de8de9417533fb28</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer - Manufacturing Plant Floor Systems</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MLOps, CI/CD, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a23c424bcc5003c2</t>
         </is>

--- a/results/job_matches_2026-10-08.xlsx
+++ b/results/job_matches_2026-10-08.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Validation Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Texas City, TX, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Azure, Data Factory, Databricks, GCP, BigQuery</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, ETL, ELT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b30786a83d421a</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb22b319ea013fb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (AWS Glue | DMS | CDC | Kafka)</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TEQDATA</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, SNS, IAM, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,19 +519,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22512bfc4565e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d52bde6426b7b2e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -540,11 +540,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52bde6426b7b2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2948fbe9d2340fca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,17 +579,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2948fbe9d2340fca</t>
+          <t>https://www.indeed.com/viewjob?jk=b0aa6dd1b04fbce5</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>AWS Cloud Application Architect - Green Card or US Citizen only</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Nextiya</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,129 +659,129 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28eca491f11ed83</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5f5b54c50c4894</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Cloud Application Architect - Green Card or US Citizen only</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nextiya</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5f5b54c50c4894</t>
+          <t>https://www.indeed.com/viewjob?jk=6ecc8f399660dece</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GroundWork Renewables, Inc.</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, USA USA</t>
+          <t>Leawood, KS, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6dd2f1d6844211</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5dc654cacc73fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AWS Agentic AI Engineer – Snowflake</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Global High Solutions</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Snowflake, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24d04fca23f04a4</t>
+          <t>https://www.indeed.com/viewjob?jk=21725d4d5a969dd0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Leawood, KS, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Scala, Kafka, PostgreSQL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,67 +799,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5dc654cacc73fe</t>
+          <t>https://www.indeed.com/viewjob?jk=415b6d66e75228d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Kansas City, MO, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab03e483c84aee8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a2d2e8f143d7289</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Platform Engineer Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>St. Louis, MO, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Snowflake, dbt, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21725d4d5a969dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=98d8a4cf8d1aaf1e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>engineer sr - ST (Hybrid) Seattle WA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Scala, Kafka, PostgreSQL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415b6d66e75228d2</t>
+          <t>https://www.indeed.com/viewjob?jk=679a365e45ca5a6c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Engineer Consultant</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, ETL</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d8a4cf8d1aaf1e</t>
+          <t>https://www.indeed.com/viewjob?jk=941ac528d3de9bd2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Erlanger, KY, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,24 +974,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50c7dd606761e70</t>
+          <t>https://www.indeed.com/viewjob?jk=2abeb02a0e515f8a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>AJAY K- SOLUTION ARCHITECT | CLOUD, DATA, INTEGRATION &amp; AI-ENABLED PLATFORMS.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Predictive Sales A.I.</t>
+          <t>Cassco International, Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Farmington Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,42 +999,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Dask, Polars, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1a6eaf40c260e</t>
+          <t>https://www.indeed.com/viewjob?jk=9af1985824c8bc86</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>engineer sr - ST (Hybrid) Seattle WA</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,137 +1044,137 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679a365e45ca5a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b919d7fa31ebc26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AJAY K- SOLUTION ARCHITECT | CLOUD, DATA, INTEGRATION &amp; AI-ENABLED PLATFORMS.</t>
+          <t>Cloud &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cassco International, Inc</t>
+          <t>Novacis Digital</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af1985824c8bc86</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2798550649837e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C,C++, Python, Golang Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Shift4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Center Valley, PA, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Scala, Polars, Snowflake, Time Travel, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aaed4db41a0b1f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b6651c19d8dca5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C++, Python, Golang Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Shift4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Scala, Polars, Snowflake, Time Travel, dbt, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4079e0cd8f01503b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6edb1d735ef07e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Orlando, FL, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abeb02a0e515f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb015cbf7890d8a1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Sterling, VA, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,102 +1219,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b919d7fa31ebc26</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbfc9f6705769bd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud &amp; Security Engineer</t>
+          <t>Senior Software Engineer I (Data Pipelines)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Novacis Digital</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2798550649837e</t>
+          <t>https://www.indeed.com/viewjob?jk=77f88462ba46b951</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Research Application Support Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd00f0bef8bd3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7aec8d989d23632c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Enterprise Database Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>BerryDunn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, USA USA</t>
+          <t>Portland, ME, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, MySQL, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,102 +1324,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea336bd03fc8adb1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc69b0c8fcdb4fa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orlando, FL, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb015cbf7890d8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa3a48755605f28e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Loveland, CO)</t>
+          <t>Senior DBA II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Antech Diagnostics</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loveland, CO, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12afaeb4d5194deb</t>
+          <t>https://www.indeed.com/viewjob?jk=acdebbbdc22b8477</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Platform Engineer/DevOp</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FedEx Dataworks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c13abcae168f92</t>
+          <t>https://www.indeed.com/viewjob?jk=75c1b2b06cb6b3d3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SDC WAMT Back End Engineer---Analyst---Dallas, Raleigh, San Antonio</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,129 +1464,129 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c11d949a142a620</t>
+          <t>https://www.indeed.com/viewjob?jk=3c365530d5e90342</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Enterprise Database Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BerryDunn</t>
+          <t>Formlabs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portland, ME, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, MySQL, ETL, ELT, Tableau</t>
+          <t>Redshift, IAM, RDS, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc69b0c8fcdb4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8e3bb316c3ab91</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DBA II</t>
+          <t>Data Engineer-5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa3a48755605f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb72edaec6cad88</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DBA II</t>
+          <t>Salesforce Developer with python-5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acdebbbdc22b8477</t>
+          <t>https://www.indeed.com/viewjob?jk=40fe46976f1c74ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Senior Data &amp; AI Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FedEx Dataworks</t>
+          <t>MojoTech</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c1b2b06cb6b3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f4183923fb92626d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>AI Solutions Engineer - Experienced</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Richmond, VA, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,172 +1639,172 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c365530d5e90342</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea0ba520f11fee7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McKinney, TX, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f610986642a7b2</t>
+          <t>https://www.indeed.com/viewjob?jk=63d4e3867310a550</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETDP Associate - Data Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Formlabs</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e3bb316c3ab91</t>
+          <t>https://www.indeed.com/viewjob?jk=cc612453c81627d3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer-5</t>
+          <t>Advisor-Data Engineer MDM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb72edaec6cad88</t>
+          <t>https://www.indeed.com/viewjob?jk=efe237925fb7924c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Salesforce Developer with python-5</t>
+          <t>Sr Advisor-Data Engineer MDM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Polars</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40fe46976f1c74ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f57eec5ffd5808ad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SDC WAMT Senior Backend Engineer---Senior-----Dallas, Raleigh, San Antonio</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Agama Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Glendale, CA, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,102 +1814,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65c5560ca576a10</t>
+          <t>https://www.indeed.com/viewjob?jk=7575f45f137226ab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Architect</t>
+          <t>Full Stack Engineer – ReactJS / Python / SQL Server</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MojoTech</t>
+          <t>Foresight IT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, Databricks, Spark, Scala</t>
+          <t>S3, API Gateway, Azure, Scala, SQL Server, Data Modeling, REST API integration, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4183923fb92626d</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab9dc0adc464b1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer - Experienced</t>
+          <t>Data &amp; Analytics Developer II - Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>Wet Coast Logistics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, USA USA</t>
+          <t>Greenville, SC, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, ETL, Power BI, MLOps, MLflow, pytest</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea0ba520f11fee7</t>
+          <t>https://www.indeed.com/viewjob?jk=4930ffb452c6e901</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DFUSE TECHNOLOGIES</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ai, OH, USA USA</t>
+          <t>Lancaster, PA, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, ELT, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,102 +1919,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3ef12034fb6c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=b81c606945103730</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer (Remote)</t>
+          <t>Full-Stack Engineer 4 (SQL Server DBA)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Revenue Management Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, USA USA</t>
+          <t>Riverwoods, IL, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83625117c0bb978</t>
+          <t>https://www.indeed.com/viewjob?jk=f393fa8d32e16893</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Advisor-Data Engineer MDM</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FedEx Freight</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Bethesda, MD, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe237925fb7924c</t>
+          <t>https://www.indeed.com/viewjob?jk=a57b9b0b5d74551c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Advisor-Data Engineer MDM</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FedEx Freight</t>
+          <t>Naviga Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,102 +2024,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57eec5ffd5808ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2a21fac0f0100e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Agama Solutions</t>
+          <t>Curant Health Georgia LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Glendale, CA, USA USA</t>
+          <t>Smyrna, GA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7575f45f137226ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f2fb1b8f4b0f0b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Full Stack Developer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>BAM Technologies, LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lancaster, PA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, ELT, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81c606945103730</t>
+          <t>https://www.indeed.com/viewjob?jk=12b4ba48e48f905c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (SQL Server DBA)</t>
+          <t>Senior Digital Banking Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, USA USA</t>
+          <t>Chelmsford, MA, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f393fa8d32e16893</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a5dfa62a0d990</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Targan INC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Blob Storage, GCP, Hive, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57b9b0b5d74551c</t>
+          <t>https://www.indeed.com/viewjob?jk=8982f49fab0f79cf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Integration Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Curant Health Georgia LLC</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Smyrna, GA, USA USA</t>
+          <t>Fort Worth, TX, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,34 +2189,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f2fb1b8f4b0f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=18b236860653562b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Senior Data Engineer</t>
+          <t>Sr. Python Developer w/d banking domain Exp in Jersey City, NJ – 5 Days Onsite</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>SGN Global Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,34 +2224,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16371cbe9a6f6a94</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e855da5922ac48</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Digital Banking Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>First Tech Federal Credit Union</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chelmsford, MA, USA USA</t>
+          <t>Buffalo, NY, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,34 +2259,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Lambda, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a5dfa62a0d990</t>
+          <t>https://www.indeed.com/viewjob?jk=53b4524a4f891c31</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Vision Software Engineer</t>
+          <t>Senior AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Targan INC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Eden Prairie, MN, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Blob Storage, GCP, Hive, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,94 +2304,94 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8982f49fab0f79cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8277a6ad907dfe29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Integration Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b236860653562b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2cfdc750e170ad</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer-Xumo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Buffalo, NY, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, BigQuery, Spark, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b4524a4f891c31</t>
+          <t>https://www.indeed.com/viewjob?jk=1d075be1566febf4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer-Xumo</t>
+          <t>Integration Engineer 4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Riverwoods, IL, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Spark, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d075be1566febf4</t>
+          <t>https://www.indeed.com/viewjob?jk=00c18c2f7ae91a00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Integration Engineer 4</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00c18c2f7ae91a00</t>
+          <t>https://www.indeed.com/viewjob?jk=31e7731f1f9f1fba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Databricks architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>RM SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e7731f1f9f1fba</t>
+          <t>https://www.indeed.com/viewjob?jk=84d787c2acfd2551</t>
         </is>
       </c>
     </row>
@@ -2521,17 +2521,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IT Analyst III - Cloud Automation and Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>Rational Dynamics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Taylorsville, UT, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9184edf09372f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b09df58bdb608c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III – AI-Centric Application Performance &amp; FinOps</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Mindbody</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,34 +2574,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Scala, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc60f244ee03aef</t>
+          <t>https://www.indeed.com/viewjob?jk=3f824146c3510fa4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Production Engineer - Realtime Products</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rational Dynamics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,34 +2609,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Oracle, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b09df58bdb608c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75f442e4703aad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>MTS 1, Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rezilient Health</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba5d9d223a8fba0</t>
+          <t>https://www.indeed.com/viewjob?jk=98bd8d73e2e92638</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer III - ETL</t>
+          <t>Senior Consultant - Data Strategy and Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Clear Base Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Cary, NC, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Scala, Oracle, NoSQL, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b8fa5e3eb4a90c</t>
+          <t>https://www.indeed.com/viewjob?jk=a660c8397fa50076</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Production Engineer - Realtime Products</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Eagan, MN, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,34 +2714,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75f442e4703aad</t>
+          <t>https://www.indeed.com/viewjob?jk=81a7de6eda101af3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Solutions Architect (Data)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, USA USA</t>
+          <t>MO, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bd8d73e2e92638</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c96a2380ee98e7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Strategy and Engineering</t>
+          <t>Tech-BAIN Service Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Clear Base Group</t>
+          <t>Universal Music Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cary, NC, USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,139 +2784,139 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a660c8397fa50076</t>
+          <t>https://www.indeed.com/viewjob?jk=b959e0e3c13d4ea3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eagan, MN, USA USA</t>
+          <t>Willow Grove, PA, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a7de6eda101af3</t>
+          <t>https://www.indeed.com/viewjob?jk=113b0ef7bbd43b1b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Architect (Data)</t>
+          <t>MTS 1, Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MO, USA USA</t>
+          <t>San Jose, CA, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Talend</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, MongoDB, Cassandra, Docker, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c96a2380ee98e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b54fe6ade52e7b03</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tech-BAIN Service Reliability Engineer</t>
+          <t>Applied AI &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Universal Music Group</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>Milwaukee, WI, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Docker, Kubernetes, Git, Java</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b959e0e3c13d4ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=be186d5b6e7e5d03</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Full stack software engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Willow Grove, PA, USA USA</t>
+          <t>Milwaukee, WI, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,34 +2924,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113b0ef7bbd43b1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef7970decc80bb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Liberty company insurance brokers</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, USA USA</t>
+          <t>Woodland Hills, CA, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,34 +2959,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, MongoDB, Cassandra, Docker, Airflow</t>
+          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54fe6ade52e7b03</t>
+          <t>https://www.indeed.com/viewjob?jk=6cea5cc81a279b30</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Applied AI &amp; Integrations Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Enable Dental</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,34 +2994,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Docker, Kubernetes, Git, Java</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be186d5b6e7e5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b35f71127e713c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full stack software engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Surge InfoTech LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, USA USA</t>
+          <t>Alexandria, VA, USA USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3029,34 +3029,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef7970decc80bb</t>
+          <t>https://www.indeed.com/viewjob?jk=009031cd529e79e4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - CTO innovations</t>
+          <t>Senior DataBricks Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NomiSo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA USA</t>
+          <t>Scottsdale, AZ, USA USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3064,34 +3064,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, ELT, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb6bdbcc89b8901</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7372a5249c25b1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Surge InfoTech LLC</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alexandria, VA, USA USA</t>
+          <t>Buffalo, NY, USA USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3099,34 +3099,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009031cd529e79e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e479aec834dda7f8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior DataBricks Engineer</t>
+          <t>Senior Software Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NomiSo</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, USA USA</t>
+          <t>Buffalo, NY, USA USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3134,34 +3134,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7372a5249c25b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac197ebe84b27d67</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer - Snowflake</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>12 Elements Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Buffalo, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,34 +3169,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e479aec834dda7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=961c09494cecca9b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Snowflake</t>
+          <t>Sr. Software Engineer (Data &amp; Integrations Engineering)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Cedar INC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Buffalo, NY, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,34 +3204,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, ETL, CI/CD, Terraform, pytest</t>
+          <t>RDS, Medallion Architecture, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac197ebe84b27d67</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a64073f77de1fc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Data &amp; Integrations Engineering)</t>
+          <t>Enterprise Software Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cedar INC</t>
+          <t>Dartmouth College</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Hanover, NH, USA USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a64073f77de1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=147e1a8f49587d0f</t>
         </is>
       </c>
     </row>
@@ -3291,17 +3291,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,34 +3309,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389bda3afea947e0</t>
+          <t>https://www.indeed.com/viewjob?jk=68f0e55cdb56404f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business (Fintech)</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Strategic Operational Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NJ, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3344,34 +3344,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95aea0382d2db66</t>
+          <t>https://www.indeed.com/viewjob?jk=aa47a8ff9ab65e1a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Quality Analyst</t>
+          <t>Microsoft Dynamics 365 F&amp;O Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Group</t>
+          <t>Innova Software Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3379,34 +3379,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f52a8d71cbe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=99b94a3a4f9e025c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics 365 F&amp;O Data Architect</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Innova Software Services</t>
+          <t>ALTEN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Foster City, CA, USA USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b94a3a4f9e025c</t>
+          <t>https://www.indeed.com/viewjob?jk=177cc6a11c4d3854</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr. Systems Engineer - Manufacturing Plant Floor Systems</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ALTEN</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Foster City, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3484,50 +3484,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MLOps, CI/CD, SonarQube, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=177cc6a11c4d3854</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer - Manufacturing Plant Floor Systems</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Austin, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MLOps, CI/CD, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a23c424bcc5003c2</t>
         </is>
